--- a/data/trans_bre/P26-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P26-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 12,38</t>
+          <t>-1,31; 12,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 10,72</t>
+          <t>-5,32; 9,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 10,56</t>
+          <t>-1,86; 10,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 4,64</t>
+          <t>-3,31; 4,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 63,48</t>
+          <t>-6,03; 64,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 43,05</t>
+          <t>-17,08; 37,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 65,17</t>
+          <t>-9,06; 66,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 66,51</t>
+          <t>-30,66; 63,16</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 20,57</t>
+          <t>6,32; 21,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 12,94</t>
+          <t>-1,61; 12,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 9,49</t>
+          <t>-3,39; 9,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 7,95</t>
+          <t>-1,86; 8,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,63; 104,67</t>
+          <t>23,23; 111,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 55,48</t>
+          <t>-5,29; 55,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 56,05</t>
+          <t>-14,33; 59,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 116,97</t>
+          <t>-20,47; 118,04</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 24,68</t>
+          <t>7,08; 24,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 17,16</t>
+          <t>2,71; 17,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 4,53</t>
+          <t>-12,0; 4,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 1,89</t>
+          <t>-69,77; 2,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,43; 95,68</t>
+          <t>23,42; 93,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 54,39</t>
+          <t>7,73; 55,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 20,87</t>
+          <t>-43,61; 19,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-95,25; 21,19</t>
+          <t>-93,56; 26,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 18,61</t>
+          <t>9,14; 18,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,47</t>
+          <t>4,04; 13,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 7,27</t>
+          <t>-1,23; 7,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 6,4</t>
+          <t>-8,57; 6,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,77; 69,92</t>
+          <t>30,78; 70,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,98; 43,18</t>
+          <t>11,61; 41,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 29,11</t>
+          <t>-4,4; 29,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 52,71</t>
+          <t>-54,44; 48,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 18,63</t>
+          <t>5,06; 18,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 13,66</t>
+          <t>1,85; 13,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 11,05</t>
+          <t>1,6; 11,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 4,59</t>
+          <t>-5,58; 4,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,72; 65,43</t>
+          <t>14,32; 68,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 44,51</t>
+          <t>6,37; 46,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 50,87</t>
+          <t>5,69; 53,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 38,7</t>
+          <t>-33,41; 40,98</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,59; -6,96</t>
+          <t>-18,62; -5,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 1,87</t>
+          <t>-11,76; 2,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,98; -4,11</t>
+          <t>-16,43; -3,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 4,26</t>
+          <t>-12,59; 4,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,61; -17,03</t>
+          <t>-37,64; -15,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 4,94</t>
+          <t>-24,28; 6,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,78; -13,61</t>
+          <t>-41,87; -12,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,51; 49,24</t>
+          <t>-53,74; 64,18</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,75</t>
+          <t>6,19; 10,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 8,5</t>
+          <t>3,51; 8,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,5</t>
+          <t>-0,73; 3,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 2,09</t>
+          <t>-25,27; 1,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,88; 39,33</t>
+          <t>20,55; 39,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,85; 26,85</t>
+          <t>10,27; 26,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 14,34</t>
+          <t>-2,7; 15,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-68,74; 17,68</t>
+          <t>-66,44; 16,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P26-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P26-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 12,55</t>
+          <t>-0,25; 12,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 9,66</t>
+          <t>-4,74; 10,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 10,83</t>
+          <t>-2,22; 10,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 4,41</t>
+          <t>-2,96; 4,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 64,98</t>
+          <t>-1,62; 67,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 37,04</t>
+          <t>-14,99; 41,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 66,91</t>
+          <t>-10,66; 64,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 63,16</t>
+          <t>-25,73; 67,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 21,03</t>
+          <t>6,59; 20,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 12,8</t>
+          <t>-1,74; 13,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 9,78</t>
+          <t>-3,27; 9,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 8,39</t>
+          <t>0,34; 8,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 111,41</t>
+          <t>23,42; 109,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 55,23</t>
+          <t>-5,62; 58,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 59,0</t>
+          <t>-14,64; 53,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 118,04</t>
+          <t>2,52; 148,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-35,35</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-80,39%</t>
+          <t>-2,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 24,3</t>
+          <t>7,05; 24,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 17,38</t>
+          <t>2,03; 17,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 4,6</t>
+          <t>-11,34; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-69,77; 2,12</t>
+          <t>-4,59; 4,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,42; 93,36</t>
+          <t>21,66; 91,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 55,27</t>
+          <t>6,3; 56,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,61; 19,97</t>
+          <t>-41,77; 17,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-93,56; 26,43</t>
+          <t>-44,35; 72,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 18,53</t>
+          <t>9,26; 19,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,16</t>
+          <t>4,04; 13,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 7,49</t>
+          <t>-1,35; 7,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 6,1</t>
+          <t>1,06; 8,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,78; 70,46</t>
+          <t>31,52; 73,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 41,65</t>
+          <t>11,32; 43,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 29,78</t>
+          <t>-4,79; 28,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,44; 48,29</t>
+          <t>6,85; 72,85</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 18,99</t>
+          <t>4,72; 18,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 13,53</t>
+          <t>1,43; 13,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 11,49</t>
+          <t>0,88; 10,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 4,64</t>
+          <t>-3,04; 5,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,32; 68,05</t>
+          <t>13,09; 67,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 46,0</t>
+          <t>3,98; 44,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 53,22</t>
+          <t>3,65; 52,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 40,98</t>
+          <t>-18,51; 46,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-2,79</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-18,61%</t>
+          <t>-19,47%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,62; -5,99</t>
+          <t>-18,99; -6,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 2,28</t>
+          <t>-11,25; 2,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,43; -3,74</t>
+          <t>-17,1; -3,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 4,96</t>
+          <t>-11,91; 4,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,64; -15,26</t>
+          <t>-37,61; -16,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 6,3</t>
+          <t>-23,9; 5,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,87; -12,35</t>
+          <t>-42,55; -13,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 64,18</t>
+          <t>-53,71; 51,67</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,77</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-31,07%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,84</t>
+          <t>5,8; 10,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,37</t>
+          <t>3,64; 8,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,69</t>
+          <t>-0,8; 3,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 1,97</t>
+          <t>0,3; 4,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,55; 39,44</t>
+          <t>19,33; 39,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,27; 26,49</t>
+          <t>10,63; 26,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 15,52</t>
+          <t>-2,93; 15,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-66,44; 16,9</t>
+          <t>2,49; 39,15</t>
         </is>
       </c>
     </row>
